--- a/MC4010_E23.xlsx
+++ b/MC4010_E23.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E28417B-B66F-4398-9A48-6AD530314A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331132BE-F5E5-4318-9E2B-3C52AD3111FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F03100B9-AA1E-4F03-9693-2922BD893DB1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>Name</t>
   </si>
@@ -313,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -345,23 +345,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -715,9 +707,15 @@
       <c r="C2" s="7">
         <v>74</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="D2" s="15">
+        <v>46</v>
+      </c>
+      <c r="E2" s="15">
+        <v>21</v>
+      </c>
+      <c r="F2" s="15">
+        <v>50</v>
+      </c>
       <c r="G2" s="7">
         <v>56</v>
       </c>
@@ -736,9 +734,15 @@
       <c r="C3" s="7">
         <v>56</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="D3" s="15">
+        <v>41</v>
+      </c>
+      <c r="E3" s="15">
+        <v>26</v>
+      </c>
+      <c r="F3" s="15">
+        <v>53</v>
+      </c>
       <c r="G3" s="7">
         <v>45</v>
       </c>
@@ -757,9 +761,15 @@
       <c r="C4" s="7">
         <v>76</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="15">
+        <v>79</v>
+      </c>
+      <c r="E4" s="15">
+        <v>26</v>
+      </c>
+      <c r="F4" s="15">
+        <v>73</v>
+      </c>
       <c r="G4" s="7">
         <v>50</v>
       </c>
@@ -778,9 +788,15 @@
       <c r="C5" s="7">
         <v>81</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="D5" s="15">
+        <v>35</v>
+      </c>
+      <c r="E5" s="15">
+        <v>40</v>
+      </c>
+      <c r="F5" s="15">
+        <v>45</v>
+      </c>
       <c r="G5" s="7">
         <v>58</v>
       </c>
@@ -799,9 +815,15 @@
       <c r="C6" s="7">
         <v>84</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="D6" s="15">
+        <v>63</v>
+      </c>
+      <c r="E6" s="15">
+        <v>41</v>
+      </c>
+      <c r="F6" s="15">
+        <v>68</v>
+      </c>
       <c r="G6" s="7">
         <v>75</v>
       </c>
@@ -820,9 +842,15 @@
       <c r="C7" s="7">
         <v>94</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="D7" s="15">
+        <v>77</v>
+      </c>
+      <c r="E7" s="15">
+        <v>65</v>
+      </c>
+      <c r="F7" s="15">
+        <v>78</v>
+      </c>
       <c r="G7" s="7">
         <v>77</v>
       </c>
@@ -841,9 +869,15 @@
       <c r="C8" s="7">
         <v>73</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="D8" s="15">
+        <v>48</v>
+      </c>
+      <c r="E8" s="15">
+        <v>23</v>
+      </c>
+      <c r="F8" s="15">
+        <v>49</v>
+      </c>
       <c r="G8" s="7">
         <v>47</v>
       </c>
@@ -862,9 +896,15 @@
       <c r="C9" s="7">
         <v>91</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="D9" s="15">
+        <v>62</v>
+      </c>
+      <c r="E9" s="15">
+        <v>41</v>
+      </c>
+      <c r="F9" s="15">
+        <v>70</v>
+      </c>
       <c r="G9" s="7">
         <v>68</v>
       </c>
@@ -883,9 +923,15 @@
       <c r="C10" s="7">
         <v>66</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="D10" s="15">
+        <v>64</v>
+      </c>
+      <c r="E10" s="15">
+        <v>21</v>
+      </c>
+      <c r="F10" s="15">
+        <v>74</v>
+      </c>
       <c r="G10" s="7">
         <v>67</v>
       </c>
@@ -904,9 +950,15 @@
       <c r="C11" s="7">
         <v>69</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="D11" s="15">
+        <v>59</v>
+      </c>
+      <c r="E11" s="15">
+        <v>54</v>
+      </c>
+      <c r="F11" s="15">
+        <v>41</v>
+      </c>
       <c r="G11" s="7">
         <v>55</v>
       </c>
@@ -925,9 +977,15 @@
       <c r="C12" s="7">
         <v>89</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="D12" s="15">
+        <v>32</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46</v>
+      </c>
+      <c r="F12" s="15">
+        <v>57</v>
+      </c>
       <c r="G12" s="7">
         <v>43</v>
       </c>
@@ -946,9 +1004,15 @@
       <c r="C13" s="7">
         <v>85</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="D13" s="15">
+        <v>68</v>
+      </c>
+      <c r="E13" s="15">
+        <v>36</v>
+      </c>
+      <c r="F13" s="15">
+        <v>46</v>
+      </c>
       <c r="G13" s="7">
         <v>42</v>
       </c>
@@ -967,9 +1031,15 @@
       <c r="C14" s="7">
         <v>62</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="D14" s="15">
+        <v>63</v>
+      </c>
+      <c r="E14" s="15">
+        <v>52</v>
+      </c>
+      <c r="F14" s="15">
+        <v>74</v>
+      </c>
       <c r="G14" s="7">
         <v>57</v>
       </c>
@@ -988,9 +1058,15 @@
       <c r="C15" s="7">
         <v>80</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="D15" s="15">
+        <v>47</v>
+      </c>
+      <c r="E15" s="15">
+        <v>24</v>
+      </c>
+      <c r="F15" s="15">
+        <v>64</v>
+      </c>
       <c r="G15" s="7">
         <v>57</v>
       </c>
@@ -1009,9 +1085,15 @@
       <c r="C16" s="7">
         <v>84</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="D16" s="15">
+        <v>58</v>
+      </c>
+      <c r="E16" s="15">
+        <v>20</v>
+      </c>
+      <c r="F16" s="15">
+        <v>55</v>
+      </c>
       <c r="G16" s="7">
         <v>63</v>
       </c>
@@ -1030,9 +1112,15 @@
       <c r="C17" s="7">
         <v>83</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="D17" s="15">
+        <v>91</v>
+      </c>
+      <c r="E17" s="15">
+        <v>90</v>
+      </c>
+      <c r="F17" s="15">
+        <v>84</v>
+      </c>
       <c r="G17" s="7">
         <v>88</v>
       </c>
@@ -1051,9 +1139,15 @@
       <c r="C18" s="7">
         <v>61</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="D18" s="15">
+        <v>44</v>
+      </c>
+      <c r="E18" s="15">
+        <v>19</v>
+      </c>
+      <c r="F18" s="15">
+        <v>86</v>
+      </c>
       <c r="G18" s="7">
         <v>58</v>
       </c>
@@ -1072,9 +1166,15 @@
       <c r="C19" s="7">
         <v>64</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="D19" s="15">
+        <v>53</v>
+      </c>
+      <c r="E19" s="15">
+        <v>30</v>
+      </c>
+      <c r="F19" s="15">
+        <v>71</v>
+      </c>
       <c r="G19" s="7">
         <v>47</v>
       </c>
@@ -1093,9 +1193,15 @@
       <c r="C20" s="7">
         <v>59</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="D20" s="15">
+        <v>42</v>
+      </c>
+      <c r="E20" s="15">
+        <v>66</v>
+      </c>
+      <c r="F20" s="15">
+        <v>64</v>
+      </c>
       <c r="G20" s="7">
         <v>71</v>
       </c>
@@ -1114,9 +1220,15 @@
       <c r="C21" s="7">
         <v>64</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="D21" s="15">
+        <v>42</v>
+      </c>
+      <c r="E21" s="15">
+        <v>22</v>
+      </c>
+      <c r="F21" s="15">
+        <v>43</v>
+      </c>
       <c r="G21" s="7">
         <v>82</v>
       </c>
@@ -1135,9 +1247,15 @@
       <c r="C22" s="7">
         <v>71</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="D22" s="15">
+        <v>48</v>
+      </c>
+      <c r="E22" s="15">
+        <v>27</v>
+      </c>
+      <c r="F22" s="15">
+        <v>63</v>
+      </c>
       <c r="G22" s="7">
         <v>25</v>
       </c>
@@ -1156,9 +1274,15 @@
       <c r="C23" s="7">
         <v>43</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="D23" s="15">
+        <v>46</v>
+      </c>
+      <c r="E23" s="15">
+        <v>12</v>
+      </c>
+      <c r="F23" s="15">
+        <v>55</v>
+      </c>
       <c r="G23" s="7">
         <v>25</v>
       </c>
@@ -1177,9 +1301,15 @@
       <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="D24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>47</v>
+      </c>
       <c r="G24" s="7">
         <v>31</v>
       </c>
@@ -1195,9 +1325,15 @@
       <c r="C25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="D25" s="15">
+        <v>59</v>
+      </c>
+      <c r="E25" s="15">
+        <v>91</v>
+      </c>
+      <c r="F25" s="15">
+        <v>63</v>
+      </c>
       <c r="G25" s="7">
         <v>39</v>
       </c>
@@ -1213,9 +1349,15 @@
       <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="D26" s="15">
+        <v>51</v>
+      </c>
+      <c r="E26" s="15">
+        <v>71</v>
+      </c>
+      <c r="F26" s="15">
+        <v>50</v>
+      </c>
       <c r="G26" s="7">
         <v>42</v>
       </c>
@@ -1231,9 +1373,15 @@
       <c r="C27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="D27" s="15">
+        <v>66</v>
+      </c>
+      <c r="E27" s="15">
+        <v>87</v>
+      </c>
+      <c r="F27" s="15">
+        <v>70</v>
+      </c>
       <c r="G27" s="7">
         <v>34</v>
       </c>
@@ -1245,21 +1393,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -1436,24 +1569,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FDC3A-3D63-45B9-9E5A-8EEBE12E7060}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1470,4 +1601,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MC4010_E23.xlsx
+++ b/MC4010_E23.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331132BE-F5E5-4318-9E2B-3C52AD3111FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BCE6CD-EA33-48B6-9339-A670321EB5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F03100B9-AA1E-4F03-9693-2922BD893DB1}"/>
   </bookViews>
@@ -1257,7 +1257,7 @@
         <v>63</v>
       </c>
       <c r="G22" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H22" s="12">
         <v>94.117647058823522</v>
@@ -1393,6 +1393,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7DC5809443B914698F205EDCFE14C5C" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="910dd8289e79bf7e3b2db69aaa037196">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2592cbe8-961e-4422-8c47-4737933d0fe0" xmlns:ns3="7af58a8f-2f6f-405a-b238-befdc3c227d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecb9083a17ae33be0a7009b46db9eab7" ns2:_="" ns3:_="">
     <xsd:import namespace="2592cbe8-961e-4422-8c47-4737933d0fe0"/>
@@ -1569,22 +1584,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FDC3A-3D63-45B9-9E5A-8EEBE12E7060}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1601,21 +1618,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>